--- a/data/trans_dic/IP36A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que perciben algun tipo de pensión</t>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 20,85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12,64; 36,48</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 11,42</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 20,2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12,8; 36,22</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,97</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,74</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 27,59</t>
+          <t>3,34; 27,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 33,87</t>
+          <t>9,79; 33,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 30,97</t>
+          <t>8,45; 30,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,44</t>
+          <t>0,0; 22,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 17,93</t>
+          <t>3,22; 18,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,39; 30,41</t>
+          <t>13,32; 29,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 19,49</t>
+          <t>5,94; 19,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,27</t>
+          <t>1,62; 15,14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 15,47</t>
+          <t>3,26; 15,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 17,89</t>
+          <t>4,26; 18,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 17,21</t>
+          <t>5,57; 18,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 35,27</t>
+          <t>3,78; 32,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 13,58</t>
+          <t>2,53; 13,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 16,4</t>
+          <t>4,56; 15,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 23,09</t>
+          <t>9,59; 23,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 26,69</t>
+          <t>8,94; 26,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,98</t>
+          <t>4,03; 12,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 13,44</t>
+          <t>5,4; 13,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 17,71</t>
+          <t>8,8; 18,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,39; 26,26</t>
+          <t>7,43; 25,85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,33</t>
+          <t>0,0; 18,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,49</t>
+          <t>0,0; 12,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 44,14</t>
+          <t>12,25; 42,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 19,49</t>
+          <t>2,16; 19,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,3</t>
+          <t>3,05; 17,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 28,07</t>
+          <t>7,0; 27,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 29,89</t>
+          <t>7,31; 30,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 15,23</t>
+          <t>2,79; 14,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,47</t>
+          <t>1,62; 9,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 15,48</t>
+          <t>4,36; 16,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,74; 30,76</t>
+          <t>12,04; 30,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 29,62</t>
+          <t>5,96; 30,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 24,07</t>
+          <t>6,86; 22,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 19,76</t>
+          <t>4,17; 19,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 27,67</t>
+          <t>1,87; 27,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 22,62</t>
+          <t>2,39; 22,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 20,81</t>
+          <t>4,87; 20,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 19,62</t>
+          <t>3,22; 18,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,89</t>
+          <t>0,0; 28,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 21,88</t>
+          <t>6,57; 21,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 19,3</t>
+          <t>7,25; 18,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 16,94</t>
+          <t>5,44; 16,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 20,44</t>
+          <t>3,2; 20,33</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,51</t>
+          <t>0,0; 17,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 23,73</t>
+          <t>2,36; 21,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 22,9</t>
+          <t>2,44; 21,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,37; 85,57</t>
+          <t>14,73; 87,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,73</t>
+          <t>0,0; 23,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 19,19</t>
+          <t>2,3; 19,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,8</t>
+          <t>0,0; 17,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 57,14</t>
+          <t>6,46; 55,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,51</t>
+          <t>1,66; 14,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 16,24</t>
+          <t>3,48; 16,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 14,52</t>
+          <t>2,42; 14,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,6; 54,09</t>
+          <t>14,05; 54,2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 22,29</t>
+          <t>2,66; 24,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,21</t>
+          <t>0,0; 15,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 21,74</t>
+          <t>2,38; 22,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,99</t>
+          <t>0,0; 17,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 17,12</t>
+          <t>1,93; 17,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,4</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 39,28</t>
+          <t>10,75; 39,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 15,51</t>
+          <t>3,88; 16,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,89</t>
+          <t>1,62; 10,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,6</t>
+          <t>1,24; 11,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,84; 25,44</t>
+          <t>8,02; 24,88</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,38</t>
+          <t>1,25; 11,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,07; 24,66</t>
+          <t>9,92; 24,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,6; 20,48</t>
+          <t>5,43; 20,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 29,58</t>
+          <t>8,72; 30,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,42</t>
+          <t>0,88; 8,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,13; 16,45</t>
+          <t>5,56; 16,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,91; 35,14</t>
+          <t>15,96; 36,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 31,64</t>
+          <t>8,76; 30,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,36</t>
+          <t>1,53; 6,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,59; 17,81</t>
+          <t>8,46; 17,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,37; 25,55</t>
+          <t>12,47; 25,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,02; 26,58</t>
+          <t>10,92; 27,26</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,73</t>
+          <t>2,78; 12,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 14,01</t>
+          <t>3,89; 13,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,27</t>
+          <t>4,23; 13,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,8; 32,64</t>
+          <t>11,88; 30,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 15,81</t>
+          <t>4,54; 15,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,74; 17,59</t>
+          <t>5,96; 17,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 9,85</t>
+          <t>1,85; 11,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,95; 40,52</t>
+          <t>18,25; 41,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,14</t>
+          <t>4,76; 12,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 13,56</t>
+          <t>6,01; 13,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 10,19</t>
+          <t>3,88; 10,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,97; 33,57</t>
+          <t>18,21; 33,87</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,21</t>
+          <t>5,15; 10,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,72</t>
+          <t>7,73; 12,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,0</t>
+          <t>6,17; 10,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,3; 21,24</t>
+          <t>10,27; 21,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,66</t>
+          <t>4,95; 9,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,77</t>
+          <t>7,82; 12,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,59; 15,5</t>
+          <t>9,4; 15,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,33; 23,07</t>
+          <t>14,81; 23,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,02</t>
+          <t>5,68; 9,01</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,04</t>
+          <t>8,41; 11,84</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,64</t>
+          <t>8,7; 12,36</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,82</t>
+          <t>13,57; 21,07</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7361</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6084</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6035</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3507</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13444</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7069</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3457</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4077; 11769</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3531</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5596</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>798; 6519</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3230; 11054</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2713; 9895</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5116</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7384</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8694; 19106</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3746; 12031</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>822; 7677</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4828</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7484</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11686</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6265</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10987</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9753</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11093</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18471</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>21439</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1896; 9032</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2243; 9515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3777; 12424</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2643; 22890</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1290; 6616</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3312; 11559</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7055; 17181</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5306; 15625</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4395; 13772</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6765; 17202</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>12439; 25638</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9606; 33418</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5153</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4846</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5841</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4790</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4313</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2555; 8803</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>632; 5674</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1350; 7712</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2139; 8286</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2084; 8698</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1527; 7738</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1416; 8161</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2877; 10979</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5945; 15205</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5526</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4288</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2469</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4569</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7008</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10095</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8757</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3908</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1728; 8785</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2852; 9519</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1742; 8205</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>461; 6819</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>605; 5664</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2020; 8611</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1498; 8580</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4966</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3565; 11626</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6018; 15482</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4797; 14813</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1351; 8592</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2334</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2548</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1431</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3358</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4021</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>677; 6306</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>654; 5870</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>531; 3144</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4870</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>633; 5280</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4279</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>457; 3944</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>710; 6310</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1956; 9081</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1250; 7732</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1501; 5794</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2570</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4619</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3763</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>640; 5955</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2326</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4118</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>575; 5467</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4138</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>717; 6345</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3932</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2255; 8355</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1847; 7654</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1168; 7456</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>643; 5950</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>3619; 11230</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2827</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12017</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5409</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6849</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7915</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>13215</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>8503</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4922</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>19932</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>18625</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>733; 6753</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7505; 18722</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2589; 9699</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3429; 11813</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>647; 6066</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4453; 13097</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8591; 19471</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4215; 14890</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2020; 9227</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>13174; 26988</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12652; 25882</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>9542; 23830</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4345</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6387</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10029</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6316</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8188</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>15636</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>10661</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>14142</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>10375</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>25666</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1857; 8675</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2922; 10492</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>3385; 10505</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>5946; 15432</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3140; 11017</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>4581; 13625</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1429; 8520</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>9720; 22230</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>6477; 16805</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>9141; 20180</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6101; 16175</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>18812; 34993</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>22499</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>38497</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>29884</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>41397</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>41758</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>48051</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>44624</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>80256</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>74560</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>89448</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>15541; 30403</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>29687; 48926</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>22052; 38235</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>26728; 56756</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>15633; 29705</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>32288; 51979</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>34212; 55659</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>38180; 61063</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>35070; 55613</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>67089; 94406</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>62753; 89150</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>70319; 109177</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP36A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,85</t>
+          <t>0,0; 22,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,64; 36,48</t>
+          <t>12,76; 36,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,42</t>
+          <t>0,0; 10,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,2</t>
+          <t>0,0; 19,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 27,24</t>
+          <t>3,32; 26,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 33,5</t>
+          <t>9,41; 31,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 30,81</t>
+          <t>8,95; 31,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,21</t>
+          <t>0,0; 23,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 18,22</t>
+          <t>3,31; 18,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 29,28</t>
+          <t>13,32; 29,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 19,08</t>
+          <t>5,63; 18,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 15,14</t>
+          <t>1,47; 14,58</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 15,52</t>
+          <t>3,23; 15,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 18,06</t>
+          <t>4,12; 18,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 18,31</t>
+          <t>6,2; 17,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 32,73</t>
+          <t>3,45; 34,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 13,0</t>
+          <t>2,5; 14,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 15,91</t>
+          <t>4,15; 16,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 23,35</t>
+          <t>8,85; 22,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 26,34</t>
+          <t>9,23; 27,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 12,62</t>
+          <t>4,07; 11,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 13,72</t>
+          <t>5,33; 13,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,13</t>
+          <t>8,95; 17,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 25,85</t>
+          <t>7,22; 25,12</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,78</t>
+          <t>0,0; 20,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,18</t>
+          <t>0,0; 14,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 42,21</t>
+          <t>12,16; 42,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 19,39</t>
+          <t>2,16; 19,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 17,41</t>
+          <t>4,49; 18,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 27,12</t>
+          <t>5,34; 28,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 30,49</t>
+          <t>7,43; 29,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 14,13</t>
+          <t>3,46; 15,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,33</t>
+          <t>1,61; 9,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 16,65</t>
+          <t>4,39; 16,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 30,79</t>
+          <t>12,76; 29,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 30,32</t>
+          <t>6,21; 30,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 22,89</t>
+          <t>6,25; 22,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 19,66</t>
+          <t>4,06; 19,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 27,64</t>
+          <t>1,81; 26,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 22,42</t>
+          <t>2,37; 21,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 20,76</t>
+          <t>4,72; 20,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 18,46</t>
+          <t>3,25; 19,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,24</t>
+          <t>0,0; 31,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 21,44</t>
+          <t>6,53; 22,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 18,64</t>
+          <t>7,42; 19,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 16,79</t>
+          <t>5,22; 16,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 20,33</t>
+          <t>3,19; 20,38</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,85</t>
+          <t>0,0; 18,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 21,96</t>
+          <t>2,32; 20,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 21,88</t>
+          <t>2,44; 22,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,73; 87,14</t>
+          <t>11,78; 86,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,92</t>
+          <t>0,0; 21,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 19,2</t>
+          <t>2,28; 19,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,26</t>
+          <t>0,0; 15,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 55,7</t>
+          <t>6,74; 55,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 14,71</t>
+          <t>1,65; 16,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 16,16</t>
+          <t>3,54; 16,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 14,98</t>
+          <t>2,47; 15,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,05; 54,2</t>
+          <t>13,3; 54,34</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 24,73</t>
+          <t>2,68; 24,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,47</t>
+          <t>0,0; 17,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 22,63</t>
+          <t>2,34; 24,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,58</t>
+          <t>0,0; 16,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 17,07</t>
+          <t>1,94; 16,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 18,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,75; 39,82</t>
+          <t>10,26; 39,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 16,07</t>
+          <t>3,74; 15,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,34</t>
+          <t>1,62; 9,35</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,46</t>
+          <t>1,21; 11,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,02; 24,88</t>
+          <t>7,5; 25,11</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,48</t>
+          <t>1,24; 11,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,92; 24,74</t>
+          <t>9,79; 24,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 20,35</t>
+          <t>5,37; 20,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,72; 30,05</t>
+          <t>8,43; 29,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,29</t>
+          <t>0,88; 7,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,56; 16,35</t>
+          <t>4,97; 16,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,96; 36,17</t>
+          <t>15,03; 34,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 30,96</t>
+          <t>8,58; 31,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,99</t>
+          <t>1,63; 7,4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,46; 17,33</t>
+          <t>8,62; 17,55</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,47; 25,5</t>
+          <t>12,03; 25,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,92; 27,26</t>
+          <t>10,69; 26,78</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,99</t>
+          <t>2,77; 13,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,89; 13,96</t>
+          <t>3,5; 13,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 13,12</t>
+          <t>3,93; 13,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,88; 30,84</t>
+          <t>11,49; 31,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 15,92</t>
+          <t>4,66; 15,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,96; 17,72</t>
+          <t>5,9; 16,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 11,01</t>
+          <t>2,48; 10,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,25; 41,73</t>
+          <t>18,7; 43,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,76; 12,36</t>
+          <t>4,79; 12,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 13,27</t>
+          <t>5,89; 13,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,27</t>
+          <t>4,02; 10,09</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,21; 33,87</t>
+          <t>17,92; 33,11</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,08</t>
+          <t>5,25; 10,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,73</t>
+          <t>7,8; 12,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,71</t>
+          <t>6,29; 10,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,27; 21,81</t>
+          <t>10,79; 21,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,41</t>
+          <t>5,03; 9,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,58</t>
+          <t>7,79; 12,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,29</t>
+          <t>9,62; 15,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,81; 23,68</t>
+          <t>14,67; 23,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,01</t>
+          <t>5,78; 9,05</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,41; 11,84</t>
+          <t>8,36; 11,97</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,36</t>
+          <t>8,53; 12,41</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,57; 21,07</t>
+          <t>13,56; 20,74</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3457</t>
+          <t>0; 3672</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4077; 11769</t>
+          <t>4116; 11687</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3531</t>
+          <t>0; 3166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5596</t>
+          <t>0; 5302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>798; 6519</t>
+          <t>794; 6395</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3230; 11054</t>
+          <t>3107; 10454</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2713; 9895</t>
+          <t>2873; 10205</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5116</t>
+          <t>0; 5341</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1306; 7384</t>
+          <t>1342; 7416</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8694; 19106</t>
+          <t>8695; 19164</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3746; 12031</t>
+          <t>3548; 11540</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>822; 7677</t>
+          <t>746; 7398</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1896; 9032</t>
+          <t>1878; 9230</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2243; 9515</t>
+          <t>2171; 9532</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3777; 12424</t>
+          <t>4210; 12032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2643; 22890</t>
+          <t>2415; 24339</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1290; 6616</t>
+          <t>1270; 7185</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3312; 11559</t>
+          <t>3018; 11708</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7055; 17181</t>
+          <t>6508; 16703</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5306; 15625</t>
+          <t>5473; 16301</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4395; 13772</t>
+          <t>4441; 13030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6765; 17202</t>
+          <t>6681; 16936</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12439; 25638</t>
+          <t>12651; 25188</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9606; 33418</t>
+          <t>9326; 32471</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4790</t>
+          <t>0; 5316</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2635,52 +2635,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4313</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2555; 8803</t>
+          <t>2537; 8829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>632; 5674</t>
+          <t>633; 5698</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1350; 7712</t>
+          <t>1988; 8350</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2139; 8286</t>
+          <t>1631; 8781</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2084; 8698</t>
+          <t>2119; 8283</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1527; 7738</t>
+          <t>1894; 8451</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1416; 8161</t>
+          <t>1407; 8219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2877; 10979</t>
+          <t>2895; 11019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5945; 15205</t>
+          <t>6301; 14714</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1728; 8785</t>
+          <t>1799; 8727</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2852; 9519</t>
+          <t>2597; 9515</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1742; 8205</t>
+          <t>1696; 8216</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>461; 6819</t>
+          <t>448; 6527</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>605; 5664</t>
+          <t>598; 5516</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2020; 8611</t>
+          <t>1958; 8682</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1498; 8580</t>
+          <t>1511; 9058</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4966</t>
+          <t>0; 5538</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3565; 11626</t>
+          <t>3544; 11975</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6018; 15482</t>
+          <t>6167; 15863</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4797; 14813</t>
+          <t>4607; 14271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1351; 8592</t>
+          <t>1350; 8611</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4021</t>
+          <t>0; 4168</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>677; 6306</t>
+          <t>665; 5774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>654; 5870</t>
+          <t>654; 6011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>531; 3144</t>
+          <t>425; 3124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4870</t>
+          <t>0; 4447</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>633; 5280</t>
+          <t>627; 5369</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4279</t>
+          <t>0; 3790</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>457; 3944</t>
+          <t>478; 3941</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>710; 6310</t>
+          <t>709; 6974</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1956; 9081</t>
+          <t>1988; 9363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1250; 7732</t>
+          <t>1275; 8106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1501; 5794</t>
+          <t>1422; 5808</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>640; 5955</t>
+          <t>645; 5831</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2326</t>
+          <t>0; 2485</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4118</t>
+          <t>0; 4593</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>575; 5467</t>
+          <t>565; 5821</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>0; 4000</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>717; 6345</t>
+          <t>721; 5972</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3932</t>
+          <t>0; 4599</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2255; 8355</t>
+          <t>2154; 8285</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1847; 7654</t>
+          <t>1781; 7596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1168; 7456</t>
+          <t>1166; 6741</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>643; 5950</t>
+          <t>626; 5913</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3619; 11230</t>
+          <t>3385; 11335</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>733; 6753</t>
+          <t>731; 6643</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7505; 18722</t>
+          <t>7408; 18306</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2589; 9699</t>
+          <t>2562; 9725</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3429; 11813</t>
+          <t>3314; 11788</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>647; 6066</t>
+          <t>643; 5694</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4453; 13097</t>
+          <t>3978; 13528</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8591; 19471</t>
+          <t>8088; 18716</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4215; 14890</t>
+          <t>4125; 14991</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2020; 9227</t>
+          <t>2146; 9767</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13174; 26988</t>
+          <t>13420; 27345</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12652; 25882</t>
+          <t>12206; 25684</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9542; 23830</t>
+          <t>9341; 23405</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1857; 8675</t>
+          <t>1848; 8886</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2922; 10492</t>
+          <t>2630; 10419</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3385; 10505</t>
+          <t>3148; 10786</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5946; 15432</t>
+          <t>5751; 15806</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3140; 11017</t>
+          <t>3227; 10723</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4581; 13625</t>
+          <t>4537; 12976</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1429; 8520</t>
+          <t>1918; 8005</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9720; 22230</t>
+          <t>9959; 22955</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6477; 16805</t>
+          <t>6520; 16334</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9141; 20180</t>
+          <t>8951; 20402</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6101; 16175</t>
+          <t>6329; 15887</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18812; 34993</t>
+          <t>18513; 34203</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15541; 30403</t>
+          <t>15827; 30572</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>29687; 48926</t>
+          <t>29964; 48322</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22052; 38235</t>
+          <t>22450; 38589</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26728; 56756</t>
+          <t>28086; 55108</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15633; 29705</t>
+          <t>15861; 30825</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32288; 51979</t>
+          <t>32162; 53201</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34212; 55659</t>
+          <t>35004; 55841</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>38180; 61063</t>
+          <t>37838; 60364</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>35070; 55613</t>
+          <t>35680; 55861</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67089; 94406</t>
+          <t>66616; 95421</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62753; 89150</t>
+          <t>61533; 89457</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>70319; 109177</t>
+          <t>70261; 107481</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP36A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,44%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,79%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,12%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>22,81%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,15</t>
+          <t>3,34; 27,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 36,22</t>
+          <t>9,64; 33,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,24</t>
+          <t>9,56; 30,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,14</t>
+          <t>0,0; 22,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 26,72</t>
+          <t>0,0; 20,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,41; 31,68</t>
+          <t>12,8; 36,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 31,78</t>
+          <t>0,0; 8,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,19</t>
+          <t>0,0; 24,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 18,3</t>
+          <t>3,43; 17,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 29,37</t>
+          <t>13,39; 30,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 18,3</t>
+          <t>6,34; 19,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,58</t>
+          <t>1,9; 16,37</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,03%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,16%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 15,86</t>
+          <t>2,51; 13,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 18,09</t>
+          <t>4,27; 16,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 17,73</t>
+          <t>9,19; 23,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 34,8</t>
+          <t>8,7; 26,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 14,12</t>
+          <t>3,31; 15,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 16,12</t>
+          <t>4,13; 17,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 22,7</t>
+          <t>5,48; 17,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 27,48</t>
+          <t>11,87; 35,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 11,94</t>
+          <t>4,09; 11,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,51</t>
+          <t>4,97; 13,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 17,81</t>
+          <t>8,72; 17,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 25,12</t>
+          <t>12,04; 27,01</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14,47%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,01%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,84</t>
+          <t>2,18; 19,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>3,24; 18,3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4,9; 28,07</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7,46; 29,97</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 20,33</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,1</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12,16; 42,34</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,16; 19,48</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 18,86</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 28,74</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 29,03</t>
+          <t>12,07; 43,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 15,43</t>
+          <t>3,45; 15,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,4</t>
+          <t>1,64; 9,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 16,71</t>
+          <t>4,21; 15,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,76; 29,8</t>
+          <t>12,09; 30,89</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,29%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,27%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 30,12</t>
+          <t>2,38; 22,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 22,88</t>
+          <t>4,57; 20,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 19,69</t>
+          <t>3,86; 19,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 26,46</t>
+          <t>0,0; 34,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 21,83</t>
+          <t>5,82; 29,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 20,93</t>
+          <t>6,32; 24,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 19,48</t>
+          <t>3,75; 19,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,49</t>
+          <t>1,48; 28,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 22,08</t>
+          <t>6,56; 21,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 19,1</t>
+          <t>7,1; 19,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 16,18</t>
+          <t>5,51; 16,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 20,38</t>
+          <t>3,25; 20,77</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,95%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,5%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>47,5%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,5</t>
+          <t>0,0; 24,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 20,11</t>
+          <t>2,3; 19,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 22,41</t>
+          <t>0,0; 13,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 86,59</t>
+          <t>6,04; 56,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,84</t>
+          <t>0,0; 18,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 19,52</t>
+          <t>2,32; 23,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,29</t>
+          <t>2,41; 22,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 55,66</t>
+          <t>13,52; 83,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 16,26</t>
+          <t>1,67; 14,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 16,66</t>
+          <t>3,45; 16,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 15,7</t>
+          <t>2,46; 14,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 54,34</t>
+          <t>13,34; 53,43</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21,62%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>10,67%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 24,22</t>
+          <t>0,0; 17,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>1,87; 17,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,25</t>
+          <t>0,0; 15,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 24,09</t>
+          <t>10,3; 39,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,99</t>
+          <t>2,67; 22,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 16,07</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,18</t>
+          <t>0,0; 15,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,26; 39,48</t>
+          <t>2,42; 21,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,74; 15,95</t>
+          <t>2,73; 15,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,35</t>
+          <t>1,61; 9,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,39</t>
+          <t>1,21; 10,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,5; 25,11</t>
+          <t>7,46; 24,79</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24,55%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4,81%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15,88%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11,35%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,55%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,29</t>
+          <t>0,88; 8,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,79; 24,2</t>
+          <t>5,13; 16,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,37; 20,4</t>
+          <t>14,91; 35,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,43; 29,99</t>
+          <t>9,41; 32,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,78</t>
+          <t>1,25; 11,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,89</t>
+          <t>10,07; 24,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,03; 34,77</t>
+          <t>5,6; 20,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 31,17</t>
+          <t>8,91; 30,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,4</t>
+          <t>1,58; 7,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 17,55</t>
+          <t>8,59; 17,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,03; 25,31</t>
+          <t>12,37; 25,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 26,78</t>
+          <t>11,59; 27,53</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>6,51%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>7,98%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 13,31</t>
+          <t>4,47; 15,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 13,86</t>
+          <t>5,74; 17,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 13,47</t>
+          <t>1,72; 9,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,49; 31,59</t>
+          <t>18,32; 41,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,66; 15,49</t>
+          <t>2,76; 12,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 16,88</t>
+          <t>3,66; 14,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 10,35</t>
+          <t>4,11; 13,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,7; 43,09</t>
+          <t>11,95; 34,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,79; 12,01</t>
+          <t>4,7; 12,14</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 13,42</t>
+          <t>5,9; 13,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,09</t>
+          <t>3,8; 10,19</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,92; 33,11</t>
+          <t>18,17; 34,69</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,14</t>
+          <t>5,17; 9,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,58</t>
+          <t>7,96; 12,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,81</t>
+          <t>9,59; 15,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,79; 21,17</t>
+          <t>14,87; 23,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,77</t>
+          <t>5,2; 10,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,88</t>
+          <t>7,89; 12,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,62; 15,34</t>
+          <t>6,21; 11,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,67; 23,41</t>
+          <t>13,38; 22,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,05</t>
+          <t>5,78; 9,02</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,36; 11,97</t>
+          <t>8,41; 12,04</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,41</t>
+          <t>8,78; 12,64</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,74</t>
+          <t>15,45; 21,98</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6084</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6035</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>7361</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1033</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6084</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6035</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>2554</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3672</t>
+          <t>799; 6605</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4116; 11687</t>
+          <t>3180; 11175</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3166</t>
+          <t>3070; 9946</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5302</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>794; 6395</t>
+          <t>0; 3349</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3107; 10454</t>
+          <t>4129; 11684</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2873; 10205</t>
+          <t>0; 2774</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5341</t>
+          <t>0; 4239</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1342; 7416</t>
+          <t>1389; 7265</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8695; 19164</t>
+          <t>8738; 19847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3548; 11540</t>
+          <t>3996; 12289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>746; 7398</t>
+          <t>685; 5892</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6265</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10987</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8737</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4673</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4828</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11686</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6265</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10987</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>18168</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1878; 9230</t>
+          <t>1276; 6910</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2171; 9532</t>
+          <t>3104; 11914</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4210; 12032</t>
+          <t>6764; 16992</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2415; 24339</t>
+          <t>4712; 14414</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1270; 7185</t>
+          <t>1925; 9006</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3018; 11708</t>
+          <t>2173; 9427</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6508; 16703</t>
+          <t>3719; 11679</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5473; 16301</t>
+          <t>5156; 15279</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4441; 13030</t>
+          <t>4468; 13075</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6681; 16936</t>
+          <t>6234; 16850</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12651; 25188</t>
+          <t>12329; 25041</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9326; 32471</t>
+          <t>11752; 26362</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4212</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1522</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1418</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5153</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2530</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4106</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4423</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9274</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5316</t>
+          <t>637; 5702</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>1433; 8103</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1499; 8578</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1846; 7424</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5186</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4991</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2537; 8829</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>633; 5698</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1988; 8350</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1631; 8781</t>
+          <t>0; 4423</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2119; 8283</t>
+          <t>2509; 8989</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1894; 8451</t>
+          <t>1890; 8340</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1407; 8219</t>
+          <t>1435; 8284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2895; 11019</t>
+          <t>2776; 10212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6301; 14714</t>
+          <t>5509; 14076</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2469</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4569</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4538</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5526</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4288</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2469</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4569</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3929</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1799; 8727</t>
+          <t>602; 5715</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2597; 9515</t>
+          <t>1895; 8632</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1696; 8216</t>
+          <t>1794; 9120</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>448; 6527</t>
+          <t>0; 5654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>598; 5516</t>
+          <t>1685; 8583</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1958; 8682</t>
+          <t>2627; 10009</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1511; 9058</t>
+          <t>1565; 8248</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5538</t>
+          <t>375; 7225</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3544; 11975</t>
+          <t>3556; 11865</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6167; 15863</t>
+          <t>5900; 16035</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4607; 14271</t>
+          <t>4858; 14941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1350; 8611</t>
+          <t>1359; 8679</t>
         </is>
       </c>
     </row>
@@ -2915,32 +2915,32 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1431</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1341</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2334</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2548</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1431</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3269</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4168</t>
+          <t>0; 5035</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>665; 5774</t>
+          <t>632; 5279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>654; 6011</t>
+          <t>0; 3420</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>425; 3124</t>
+          <t>427; 3987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4447</t>
+          <t>0; 4170</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>627; 5369</t>
+          <t>666; 6813</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3790</t>
+          <t>646; 6142</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>478; 3941</t>
+          <t>500; 3091</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>709; 6974</t>
+          <t>715; 6225</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1988; 9363</t>
+          <t>1940; 9130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1275; 8106</t>
+          <t>1267; 7493</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1422; 5808</t>
+          <t>1435; 5750</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2570</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>477</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1316</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2664</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>5910</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>645; 5831</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2485</t>
+          <t>697; 6364</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4593</t>
+          <t>0; 3895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>565; 5821</t>
+          <t>1899; 7249</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4000</t>
+          <t>643; 5368</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>721; 5972</t>
+          <t>0; 2211</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4599</t>
+          <t>0; 4051</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2154; 8285</t>
+          <t>575; 5042</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1781; 7596</t>
+          <t>1299; 7385</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1166; 6741</t>
+          <t>1158; 7137</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>626; 5913</t>
+          <t>628; 5502</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3385; 11335</t>
+          <t>3150; 10466</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7915</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13215</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7982</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>2827</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>12017</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>5409</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>6849</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2094</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7915</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13215</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>14951</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>731; 6643</t>
+          <t>646; 6160</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7408; 18306</t>
+          <t>4112; 13175</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2562; 9725</t>
+          <t>8027; 18915</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3314; 11788</t>
+          <t>3918; 13603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>643; 5694</t>
+          <t>735; 6693</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3978; 13528</t>
+          <t>7615; 18655</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8088; 18716</t>
+          <t>2671; 9763</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4125; 14991</t>
+          <t>3425; 11660</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2146; 9767</t>
+          <t>2092; 9713</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13420; 27345</t>
+          <t>13380; 27744</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12206; 25684</t>
+          <t>12559; 25931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9341; 23405</t>
+          <t>9279; 22050</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6316</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8188</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>16340</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>4345</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>5954</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>6387</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>10029</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>6316</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>8188</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3987</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>25666</t>
+          <t>27314</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1848; 8886</t>
+          <t>3092; 10942</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2630; 10419</t>
+          <t>4411; 13527</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3148; 10786</t>
+          <t>1330; 7617</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5751; 15806</t>
+          <t>10051; 22603</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3227; 10723</t>
+          <t>1843; 8497</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4537; 12976</t>
+          <t>2753; 10529</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1918; 8005</t>
+          <t>3291; 10626</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9959; 22955</t>
+          <t>6364; 18574</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6520; 16334</t>
+          <t>6393; 16503</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8951; 20402</t>
+          <t>8975; 20625</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6329; 15887</t>
+          <t>5987; 16041</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18513; 34203</t>
+          <t>19644; 37507</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>41758</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>45431</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>22499</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>38497</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>29884</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>22125</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>41758</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>44676</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>85368</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15827; 30572</t>
+          <t>16332; 30481</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>29964; 48322</t>
+          <t>32893; 52758</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22450; 38589</t>
+          <t>34909; 56409</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28086; 55108</t>
+          <t>35136; 56314</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15861; 30825</t>
+          <t>15685; 30786</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32162; 53201</t>
+          <t>30332; 48868</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35004; 55841</t>
+          <t>22178; 39283</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>37838; 60364</t>
+          <t>30227; 51476</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>35680; 55861</t>
+          <t>35697; 55657</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66616; 95421</t>
+          <t>67069; 96012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61533; 89457</t>
+          <t>63317; 91117</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>70261; 107481</t>
+          <t>71378; 101591</t>
         </is>
       </c>
     </row>
